--- a/data/robo_sensor_key.xlsx
+++ b/data/robo_sensor_key.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/graceleuchtenberger/Library/Mobile Documents/com~apple~CloudDocs/Documents/Density_field/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{530BB148-FDE4-E24C-807D-8686D54616E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD392255-7DA0-7B4C-9A26-8DCA6D9F0EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6420" yWindow="2580" windowWidth="28040" windowHeight="17440" xr2:uid="{E5551131-2787-2048-A137-0E9CDA1D5CCA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="34">
   <si>
     <t>robo_sensor</t>
   </si>
@@ -129,6 +129,15 @@
   </si>
   <si>
     <t>rack</t>
+  </si>
+  <si>
+    <t>tide</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
 </sst>
 </file>
@@ -500,10 +509,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E258338-C224-DE46-839A-CB519B1CEFB7}">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -517,13 +526,16 @@
         <v>24</v>
       </c>
       <c r="E1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" t="s">
         <v>27</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -537,13 +549,16 @@
         <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -557,13 +572,16 @@
         <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -577,13 +595,16 @@
         <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -597,13 +618,16 @@
         <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -617,13 +641,16 @@
         <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>96</v>
       </c>
@@ -637,13 +664,16 @@
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="G7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -657,13 +687,16 @@
         <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+      <c r="G8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -677,13 +710,16 @@
         <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+      <c r="G9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -697,13 +733,16 @@
         <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+      <c r="G10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -717,13 +756,16 @@
         <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+      <c r="G11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>100</v>
       </c>
@@ -737,13 +779,16 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+      <c r="G12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -757,13 +802,16 @@
         <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="G13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -777,13 +825,16 @@
         <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="G14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -797,13 +848,16 @@
         <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="G15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -817,13 +871,16 @@
         <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="G16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -837,13 +894,16 @@
         <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="G17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -857,13 +917,16 @@
         <v>25</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+      <c r="G18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -877,13 +940,16 @@
         <v>25</v>
       </c>
       <c r="E19" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+      <c r="G19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>44</v>
       </c>
@@ -897,13 +963,16 @@
         <v>26</v>
       </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+      <c r="G20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -917,13 +986,16 @@
         <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F21" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+      <c r="G21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -937,13 +1009,16 @@
         <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+      <c r="G22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>46</v>
       </c>
@@ -957,9 +1032,12 @@
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" t="s">
         <v>25</v>
       </c>
     </row>

--- a/data/robo_sensor_key.xlsx
+++ b/data/robo_sensor_key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/graceleuchtenberger/Library/Mobile Documents/com~apple~CloudDocs/Documents/Density_field/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD392255-7DA0-7B4C-9A26-8DCA6D9F0EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D06F226-49CE-6548-AF63-F75301708BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6420" yWindow="2580" windowWidth="28040" windowHeight="17440" xr2:uid="{E5551131-2787-2048-A137-0E9CDA1D5CCA}"/>
+    <workbookView xWindow="1360" yWindow="680" windowWidth="28040" windowHeight="17160" xr2:uid="{E5551131-2787-2048-A137-0E9CDA1D5CCA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -862,7 +862,7 @@
         <v>13</v>
       </c>
       <c r="B16">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="C16">
         <v>1</v>

--- a/data/robo_sensor_key.xlsx
+++ b/data/robo_sensor_key.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/graceleuchtenberger/Library/Mobile Documents/com~apple~CloudDocs/Documents/Density_field/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D06F226-49CE-6548-AF63-F75301708BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7C11D1-863E-8347-B3FA-9507CF924CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="680" windowWidth="28040" windowHeight="17160" xr2:uid="{E5551131-2787-2048-A137-0E9CDA1D5CCA}"/>
   </bookViews>
@@ -589,7 +589,7 @@
         <v>94</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="s">
         <v>26</v>
@@ -681,7 +681,7 @@
         <v>97</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="s">
         <v>26</v>
@@ -750,7 +750,7 @@
         <v>99</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="s">
         <v>26</v>
@@ -796,7 +796,7 @@
         <v>27</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
@@ -862,10 +862,10 @@
         <v>13</v>
       </c>
       <c r="B16">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="s">
         <v>26</v>
@@ -957,7 +957,7 @@
         <v>44</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="s">
         <v>26</v>
